--- a/artfynd/A 45267-2021 artfynd.xlsx
+++ b/artfynd/A 45267-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45267-2021 artfynd.xlsx
+++ b/artfynd/A 45267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89284447</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740240.7836949199</v>
+        <v>740241</v>
       </c>
       <c r="R2" t="n">
-        <v>7122206.212999255</v>
+        <v>7122206</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2020-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +774,821 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>117086060</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rödåborg NVO, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>740240</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7122347</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117086059</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rödåborg NVO, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>740240</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7122346</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>basen på grov gran</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89284422</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rödåborg, Överrödå, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>740302</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7122172</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hördes</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4220494</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rödåborgs naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>740321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7122151</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-05-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-05-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5031649</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rödåborgs naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>740321</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7122151</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-05-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ganska rikligt, &gt;&gt;50 plantor, fint blommande</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89284481</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rödåborg, Överrödå, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>740312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7122193</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-10-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>ungskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116897284</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rödåborgs naturreservat, Rödåborgs naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>740238</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7122330</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Glenn Örnberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>117086351</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rödåborg NVO, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>740249</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7122347</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45267-2021 artfynd.xlsx
+++ b/artfynd/A 45267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89284447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117086060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117086059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89284422</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4220494</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5031649</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89284481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116897284</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,8 +1634,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117086351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>